--- a/mes-plugins/mes-plugins-production-counting/src/main/resources/productionCounting/public/resources/productionTrackingImportSchema_pl.xlsx
+++ b/mes-plugins/mes-plugins-production-counting/src/main/resources/productionCounting/public/resources/productionTrackingImportSchema_pl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krna/Projects/mes/mes-plugins/mes-plugins-production-counting/src/main/resources/productionCounting/public/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monikajedrysiak/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A02E45D-B6DC-224B-B1C9-556EF036F3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15C7EAD7-A633-D74B-B835-A1DED9400B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1080" yWindow="-17480" windowWidth="28800" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Zlecenia produkcyjne - import" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,303 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Monika Jędrysiak</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{1F9C177A-A849-CD43-9B66-45DB9F2A7E97}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>qcadoo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>Dana wymagana. Wskaż kod zlecenia, widoczny w kolumnie w liście planowanych zleceń.Zlecenie musi być rozpoczęte.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{DF4EADDA-7FD1-AF4F-A885-A49D5D8291EA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>qcadoo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>Dana wymagana. Wskaż numer pracownika zdefiniowanego w qcadoo.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{5187C75F-FE3C-A54E-9435-8AAB7CB8B45F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>qcadoo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">Wskaż numer zmiany zdefiniowanej w qcadoo. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{AA5DE587-8413-F548-B5A0-EB20C1289363}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>qcadoo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>Dana wymagana. Wskaż datę i godzinę w formacie RRRR-MM-RR GG:MM:SS. Komórka musi mieć format tekstowy.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{1AF5A072-DA31-5042-9297-AB21A9D8F3C5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>qcadoo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dana wymagana. Wskaż datę i godzinę w formacie RRRR-MM-RR GG:MM:SS. Komórka musi mieć format tekstowy.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{121A8DE7-F22B-0943-AA51-46CC1A3F8799}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>qcadoo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>Dana wymagana. Wskaż ilość wyprodukowaną głównego produktu wyjściowego zlecenia lub operacji zlecenia.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{AC44A368-7773-534B-92F6-7708F2FEB833}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>qcadoo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>Dana opcjonalna. Wskaż ilość wyprodukowanych braków w zleceniu lub operacji zlecenia.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{E20BCA73-5751-5A43-8F85-124C040D1C9B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>qcadoo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>Dana opcjonalna. Wskaż przyczynę braków zdefiniowaną w qcadoo. Wypełnij zawsze, gdy wystąpiły braki.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -55,7 +352,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -92,6 +389,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -113,17 +431,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -181,7 +507,7 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Styl tabeli 1" pivot="0" count="1" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="4"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -837,15 +1163,19 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H2" insertRow="1" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:H2" insertRow="1" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:H2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Kod zlecenia" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Numer pracownika" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Zmiana" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Od daty"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Do daty"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Kod zlecenia" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Numer pracownika" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Zmiana" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Od daty" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Do daty" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Ilość wyprodukowana"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Braki"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Przyczyna braków"/>
@@ -1150,16 +1480,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="8" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="5" width="20.83203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="24.5" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -1172,19 +1506,19 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1197,8 +1531,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>